--- a/outputs/suratech_data_consolidado.xlsx
+++ b/outputs/suratech_data_consolidado.xlsx
@@ -9,8 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle Google Ads" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discrepancias" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recomendaciones" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolución MoM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cruces" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optimizaciones" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discrepancias" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recomendaciones" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,10 +64,15 @@
     <font>
       <b val="1"/>
       <color rgb="0000359C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000359C"/>
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +97,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,7 +147,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -533,7 +548,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Periodo: abril 2026 · Generado: 2026-04-24T21:16:08</t>
+          <t>Periodo: abril 2026 · Generado: 2026-04-24T21:38:39</t>
         </is>
       </c>
     </row>
@@ -897,7 +912,7 @@
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
@@ -998,7 +1013,7 @@
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>326,00 US$/día</t>
+          <t>$326.00/día</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -1053,7 +1068,7 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>147,00 US$/día</t>
+          <t>$147.00/día</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
@@ -1108,7 +1123,7 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>52,00 US$/día</t>
+          <t>$52.00/día</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
@@ -1163,7 +1178,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>517,00 US$/día</t>
+          <t>$517.00/día</t>
         </is>
       </c>
       <c r="F5" s="8" t="n">
@@ -1218,7 +1233,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>357,00 US$/día</t>
+          <t>$357.00/día</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
@@ -1273,7 +1288,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>183,00 US$/día</t>
+          <t>$183.00/día</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
@@ -1328,7 +1343,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>75,00 US$/día</t>
+          <t>$75.00/día</t>
         </is>
       </c>
       <c r="F8" s="10" t="n">
@@ -1383,7 +1398,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>397,00 US$/día</t>
+          <t>$397.00/día</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
@@ -1438,7 +1453,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>984,00 US$/día</t>
+          <t>$984.00/día</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
@@ -1493,7 +1508,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>900,00 US$/día</t>
+          <t>$900.00/día</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
@@ -1548,7 +1563,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>376,00 US$/día</t>
+          <t>$376.00/día</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
@@ -1603,7 +1618,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>106,00 US$/día</t>
+          <t>$106.00/día</t>
         </is>
       </c>
       <c r="F13" s="10" t="n">
@@ -1658,7 +1673,7 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>251,00 US$/día</t>
+          <t>$251.00/día</t>
         </is>
       </c>
       <c r="F14" s="10" t="n">
@@ -1713,7 +1728,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>155,00 US$/día</t>
+          <t>$155.00/día</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
@@ -1768,7 +1783,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>25,00 US$/día</t>
+          <t>$25.00/día</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
@@ -1819,7 +1834,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>10,00 US$/día</t>
+          <t>$10.00/día</t>
         </is>
       </c>
       <c r="F17" s="10" t="n">
@@ -1870,7 +1885,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>11,00 US$/día</t>
+          <t>$11.00/día</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
@@ -1925,7 +1940,7 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>29,00 US$/día</t>
+          <t>$29.00/día</t>
         </is>
       </c>
       <c r="F19" s="10" t="n">
@@ -1980,7 +1995,7 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>15,00 US$/día</t>
+          <t>$15.00/día</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
@@ -2018,6 +2033,2044 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Compromiso</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Leads CRM</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Cumplimiento %</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>CPL Negocio</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Inv. Google Ads</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Inv. Meta</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Inv. Total</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>Leads Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>enero 2026</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>8312</v>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>11398</v>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>137.1%</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>26333</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>15645.1</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>43862.31</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>12291</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>febrero 2026</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>7879</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>9883</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>125.4%</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>28539</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>17338.69</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>47315</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>10960</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>marzo 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>10130</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>9293</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>26309</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>15460.49</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>42831.72</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>9693</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>abril 2026</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>9823</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>5564</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>56.6%</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>22945</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>9112.459999999999</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>33030.43</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>6710</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Motos</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>enero 2026</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>15442</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>18115</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>117.3%</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>9167</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>9432.9</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>19872.21</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>3304</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Motos</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>febrero 2026</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>14323</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>14396</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>100.5%</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>16853</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>14370.35</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>31527.67</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Motos</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>marzo 2026</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>15442</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>12338</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>79.9%</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>17494</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>14514.97</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>32387.48</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Motos</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>abril 2026</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>14412</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>7973</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>55.3%</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>13044</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>5825.19</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>19527.48</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>enero 2026</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>24635</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>13845</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>34073</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>26509.91</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>61535.6</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>5946</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>febrero 2026</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>18769</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>11961</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>63.7%</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>18478</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>12881.58</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>31718.02</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>4783</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>marzo 2026</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>16423</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>8911</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>54.3%</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>25605</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>18838.04</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>44890.51</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>4978</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>abril 2026</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>16423</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>5285</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>32.2%</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>24344</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>7148.38</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>32387.4</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>enero 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>2280</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>1301</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>7046</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>3639.83</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>11310.18</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>febrero 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>2280</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>1239</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>54.3%</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>7097</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>4224.37</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>11439.71</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>marzo 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>2280</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>89.3%</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>7091</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>4254.02</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>11475.23</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>abril 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>2660</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>43.2%</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>5611</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>2771.74</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>8539.709999999999</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>264</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Leads CRM</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Conv. Google Ads</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Ratio GA/CRM</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Leads Meta</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Leads Otros</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Inv. GA Extractor</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Inv. GA CRM</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Δ Inversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="n">
+        <v>5564</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>4824.039999999999</v>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>2293</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>550</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>26251.95</v>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>22945</v>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>3306.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Motos</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>7973</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1043</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>15787.52</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>13044</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>2743.52</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>5285</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>2296.54</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>27828.23</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>24344</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>3484.23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>1149</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>242.66</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>6705.12</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>5611</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>1094.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>ESCALAR (CPA bajo + headroom)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Campaña</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Subtipo</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Budget/día</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Coste</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Conversiones</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>% Lost Budget</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>% Lost Rank</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>SURA_AUTOS_PMAX</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>PMAX</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>517</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>10671.24</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>2726</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Algunos grupos de recursos están limitados por una política</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>SURA_AUTOS_SEARCH_CONQUEST</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>SEARCH_CONQUEST</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>2188.75</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>340</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Apto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>SURA_AUTOS_SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>326</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>9197.959999999999</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>1364</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>Apto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>SURA_AUTOS_SEARCH_RETENTION</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>SEARCH_RETENTION</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>147</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>4194</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>393</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>Apto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>SURA_VIAJES_PMAX</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>PMAX</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>155</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>1958.94</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>86</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>Limitada por el presupuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>PAUSAR (CPA alto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Campaña</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Subtipo</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Budget/día</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Coste</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Conversiones</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>% Lost Budget</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>% Lost Rank</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>SURA_VIAJES_SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1775.47</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Apto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>SURA_ARRIENDO_SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>8208.290000000001</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>317</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Se han rechazado algunos anuncios</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>SURA_VIAJES_SEARCH_RETENTION</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>SEARCH_RETENTION</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>251</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>2970.71</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Apto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>SURA_ARRIENDO_PMAX</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>PMAX</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>376</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>7237.76</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>311</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Algunos grupos de recursos están limitados por una política</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>SURA_VIAJES_PMAX</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>PMAX</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1958.94</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Limitada por el presupuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>DESTRABAR (rechazos/políticas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Campaña</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Subtipo</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Budget/día</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Coste</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Conversiones</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>% Lost Budget</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>% Lost Rank</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>sura-cdd-co-google-search-retention-arriendo</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>SEARCH_RETENTION</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>984</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>12382.18</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1667</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Se han rechazado algunos anuncios</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>SURA_AUTOS_PMAX</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>PMAX</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>517</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>10671.24</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>2726</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Algunos grupos de recursos están limitados por una política</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>SURA_ARRIENDO_SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>900</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>8208.290000000001</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>317</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Se han rechazado algunos anuncios</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Motos</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>SURA_MOTOS_PMAX</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>PMAX</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>397</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>7831.97</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>AptoAlgunos grupos de recursos se han rechazado y Algunos grupos de recursos están limitados por una política</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>SURA_ARRIENDO_PMAX</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>PMAX</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>376</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>7237.76</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>311</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Algunos grupos de recursos están limitados por una política</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Motos</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>SURA_MOTOS_SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>357</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>4595.78</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>AptoSe han rechazado algunos anuncios</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>SURA_VIAJES_PMAX</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>PMAX</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>155</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>1958.94</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Limitada por el presupuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Salud Animal</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>SURA_SALUD_MASCOTAS_SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>283.06</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Entidad apta (limitada)Faltan suficientes palabras clave relevantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>QUALITY ISSUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Campaña</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Subtipo</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Budget/día</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Coste</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Conversiones</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>% Lost Budget</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>% Lost Rank</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Salud para Dos</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>SURA_SALUDPARADOS_SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>SEARCH_SEGMENT</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>416.3</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>Apto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>SURA_AUTOS_SEARCH_CONQUEST</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>SEARCH_CONQUEST</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>2188.75</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>340</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>Apto</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2033,7 +4086,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Discrepancias y gaps</t>
         </is>
@@ -2048,9 +4101,9 @@
       </c>
     </row>
     <row r="4" ht="50" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>PENDIENTE: el pipeline manual no logra mapear eventos GA4 -&gt; seguro automaticamente. Recomendar migrar a GA4 Data API.</t>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>PENDIENTE: GA4 Data API no integrada en MVP. Mapeo evento -&gt; seguro requiere intervencion manual via UI.</t>
         </is>
       </c>
     </row>
@@ -2063,9 +4116,9 @@
       </c>
     </row>
     <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>PARCIAL: solo capturados nombres de 4 campanias (Mensajes_WHATSAPP, Mascotas-Conversiones, Mensajes WhatsApp, Clientes potenciales). Drill-down a ad sets por seguro requiere Meta Marketing API.</t>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>PARCIAL: solo capturados nombres de 4 campanias (Mensajes_WHATSAPP, Mascotas-Conversiones, Mensajes WhatsApp, Clientes potenciales). Drill-down a ad sets requiere Meta Marketing API.</t>
         </is>
       </c>
     </row>
@@ -2078,9 +4131,9 @@
       </c>
     </row>
     <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Sin data CRM en 'Resumen mensual'. Solo tienen actividad en Google Ads / Meta (foco: potenciar).</t>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Sin data CRM en 'Resumen mensual'. Solo tienen actividad en Google Ads (foco: setear tracking + potenciar).</t>
         </is>
       </c>
     </row>
@@ -2094,7 +4147,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2168,502 +4221,502 @@
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="13" t="n">
+      <c r="A2" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>CRITICA</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>TODOS</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Reactivar las 5 cuentas con anuncios sin publicar</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>Entrar al MCC SURATECH-COLOMBIA, identificar las 5 cuentas con alerta 'anuncios no se publican' y reactivar inmediatamente. Si hay payment issue, sumar metodo de pago.</t>
-        </is>
-      </c>
-      <c r="G2" s="13" t="inlineStr">
-        <is>
-          <t>Inversion potencial parada. La alerta esta visible en el header del MCC. Cada dia sin publicar = leads perdidos imposibles de recuperar.</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Entrar al MCC SURATECH-COLOMBIA, identificar las 5 cuentas con alerta 'anuncios no se publican' y reactivar HOY. Verificar metodo de pago, billing alerts, restricciones de cuenta.</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>Inversion potencial parada. Cada dia sin publicar = leads imposibles de recuperar.</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>ALTO - posible recuperar 10-30% del ritmo de leads del mes</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="15" t="inlineStr">
         <is>
           <t>bajo</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="15" t="inlineStr">
         <is>
           <t>HOY</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="13" t="n">
+      <c r="A3" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>CRITICA</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>TODOS</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Completar verificación de servicios financieros en 3 cuentas</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>Subir documentación legal de SURA + cumplir requisitos de Google Ads para anunciantes de seguros. Hay 3 cuentas con esta alerta pendiente.</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>Bloqueante administrativo. Sin verificación, Google va a empezar a limitar/pausar delivery automaticamente.</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>MEDIO - previene caida abrupta de impresiones la semana que viene</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Subir documentacion legal de SURA + cumplir requisitos para anunciantes de seguros. 3 cuentas pendientes.</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>Bloqueante administrativo. Sin verificación, Google empieza a limitar/pausar delivery automaticamente.</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>MEDIO - previene caída abrupta de impresiones la semana que viene</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>esta semana</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>CRITICA</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Motos</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>URGENTE: Tracking de conversiones roto en Motos (Google Ads)</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Revisar el evento de conversion configurado en la cuenta Google Ads de Motos. El tag de conversion no esta disparando. Validar tag manager / GA4 conversion import. Reasignar el evento si fue eliminado.</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>En abril 2026, el CRM registra 7,973 leads de Motos pero Google Ads reporta 0 conversiones. Sin tracking, el bidding de Smart Bidding no puede optimizar - cada US$ invertido en Motos esta a ciegas.</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>ALTO - reactivar bidding optimizado puede bajar CPC -20% en 7 dias</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>hoy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>CRITICA</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Arrendamiento</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Inyectar presupuesto en Arrendamiento - gap de 11,138 leads para cumplir</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Identificar la mejor campaña SURA_ARRENDAMIENTO_* por CPA y subir presupuesto +30% por 7 dias. Reasignar de campañas low-performance del mismo seguro.</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Cumplimiento 32.2% vs 70% transcurrido del mes. Gap de 11,138 leads CRM. Sin accion, no se llega al compromiso de 16,423.0.</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>ALTO - cerrar 60% del gap</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Investigar caída de Arrendamiento: cumplimiento -40% MoM y CPL +21% MoM</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Auditar campanias SURA_ARRIENDO_*: cambios recientes en bidding, presupuesto, audiencias, palabras clave. Comparar landing pages activas vs marzo. Revisar cambios en quality score. Reactivar lo que funcionaba en febrero (CPL $2.65).</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Cumplimiento cayó de 54.3% (mes anterior) a 32.2% (mes actual). CPL Negocio subió de $5.04 a $6.13. Esto sugiere algo que se rompió en el funnel: tracking, landing, oferta o quality score.</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>ALTO - cerrar el gap de 11.138 leads requiere arreglar la causa raiz</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>esta semana</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Autos</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Inyectar presupuesto en Autos - gap 4,259 leads para cumplir compromiso</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Identificar la mejor campania SURA_AUTOS_* por CPA y subir presupuesto +30% por 7 dias. Reasignar de campanias low-performance del mismo seguro.</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>Cumplimiento 56.6% vs 70% transcurrido. Gap 4,259 leads. Sin accion no se llega al compromiso de 9,823.0.</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>ALTO - cerrar 43% del gap</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>bajo</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>hoy</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Motos</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Inyectar presupuesto en Motos - gap 6,439 leads para cumplir compromiso</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Identificar la mejor campania SURA_MOTOS_* por CPA y subir presupuesto +30% por 7 dias. Reasignar de campanias low-performance del mismo seguro.</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>Cumplimiento 55.3% vs 70% transcurrido. Gap 6,439 leads. Sin accion no se llega al compromiso de 14,412.0.</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>ALTO - cerrar 44% del gap</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>hoy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Inyectar presupuesto en Viajes - gap 1,511 leads para cumplir compromiso</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Identificar la mejor campania SURA_VIAJES_* por CPA y subir presupuesto +30% por 7 dias. Reasignar de campanias low-performance del mismo seguro.</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>Cumplimiento 43.2% vs 70% transcurrido. Gap 1,511 leads. Sin accion no se llega al compromiso de 2,660.0.</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>ALTO - cerrar 56% del gap</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>hoy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Destrabar sura-cdd-co-google-search-retention-arriendo - estado: Se han rechazado algunos anuncios</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Entrar a la campaña sura-cdd-co-google-search-retention-arriendo, revisar assets/anuncios rechazados, corregir copy o creativos según motivo de rechazo, re-someter a revision. Presupuesto activo $984.00/día.</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>Estado actual: 'Se han rechazado algunos anuncios'. Inversion ya gastada $12,382 con limitaciones - hay headroom inmediato al destrabar.</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>MEDIO - liberar 20-40% de la capacidad de la campania</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>esta semana</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Autos</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Destrabar SURA_AUTOS_PMAX - grupos limitados por política</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>Entrar a la campaña SURA_AUTOS_PMAX, revisar los assets/anuncios rechazados, corregir copy o creativos según motivo de rechazo, re-someter a revision.</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Estado actual: 'Algunos grupos de recursos están limitados por una política'. Presupuesto $517,00 US$/día parcialmente sin entregar.</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>MEDIO - liberar 20-40% de la capacidad de la campaña</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Destrabar SURA_AUTOS_PMAX - estado: Algunos grupos de recursos están limitados por una política</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Entrar a la campaña SURA_AUTOS_PMAX, revisar assets/anuncios rechazados, corregir copy o creativos según motivo de rechazo, re-someter a revision. Presupuesto activo $517.00/día.</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>Estado actual: 'Algunos grupos de recursos están limitados por una política'. Inversion ya gastada $10,671 con limitaciones - hay headroom inmediato al destrabar.</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>MEDIO - liberar 20-40% de la capacidad de la campania</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>esta semana</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Motos</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Arrendamiento</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Destrabar SURA_MOTOS_SEARCH_SEGMENT - grupos limitados por política</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>Entrar a la campaña SURA_MOTOS_SEARCH_SEGMENT, revisar los assets/anuncios rechazados, corregir copy o creativos según motivo de rechazo, re-someter a revision.</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Estado actual: 'AptoSe han rechazado algunos anuncios'. Presupuesto $357,00 US$/día parcialmente sin entregar.</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>MEDIO - liberar 20-40% de la capacidad de la campaña</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Destrabar SURA_ARRIENDO_SEARCH_SEGMENT - estado: Se han rechazado algunos anuncios</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Entrar a la campaña SURA_ARRIENDO_SEARCH_SEGMENT, revisar assets/anuncios rechazados, corregir copy o creativos según motivo de rechazo, re-someter a revision. Presupuesto activo $900.00/día.</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Estado actual: 'Se han rechazado algunos anuncios'. Inversion ya gastada $8,208 con limitaciones - hay headroom inmediato al destrabar.</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>MEDIO - liberar 20-40% de la capacidad de la campania</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>esta semana</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Motos</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Google Ads</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Destrabar SURA_MOTOS_PMAX - grupos limitados por política</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>Entrar a la campaña SURA_MOTOS_PMAX, revisar los assets/anuncios rechazados, corregir copy o creativos según motivo de rechazo, re-someter a revision.</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Estado actual: 'AptoAlgunos grupos de recursos se han rechazado y Algunos grupos de recursos están limitados por una política'. Presupuesto $397,00 US$/día parcialmente sin entregar.</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>MEDIO - liberar 20-40% de la capacidad de la campaña</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
-        <is>
-          <t>esta semana</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Arrendamiento</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Google Ads</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Destrabar sura-cdd-co-google-search-retention-arriendo - grupos limitados por política</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>Entrar a la campaña sura-cdd-co-google-search-retention-arriendo, revisar los assets/anuncios rechazados, corregir copy o creativos según motivo de rechazo, re-someter a revision.</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>Estado actual: 'Se han rechazado algunos anuncios'. Presupuesto $984,00 US$/día parcialmente sin entregar.</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>MEDIO - liberar 20-40% de la capacidad de la campaña</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="inlineStr">
-        <is>
-          <t>esta semana</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Arrendamiento</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Google Ads</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Destrabar SURA_ARRIENDO_SEARCH_SEGMENT - grupos limitados por política</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>Entrar a la campaña SURA_ARRIENDO_SEARCH_SEGMENT, revisar los assets/anuncios rechazados, corregir copy o creativos según motivo de rechazo, re-someter a revision.</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Estado actual: 'Se han rechazado algunos anuncios'. Presupuesto $900,00 US$/día parcialmente sin entregar.</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>MEDIO - liberar 20-40% de la capacidad de la campaña</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
-        <is>
-          <t>esta semana</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Arrendamiento</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Google Ads</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Destrabar SURA_ARRIENDO_PMAX - grupos limitados por política</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>Entrar a la campaña SURA_ARRIENDO_PMAX, revisar los assets/anuncios rechazados, corregir copy o creativos según motivo de rechazo, re-someter a revision.</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>Estado actual: 'Algunos grupos de recursos están limitados por una política'. Presupuesto $376,00 US$/día parcialmente sin entregar.</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>MEDIO - liberar 20-40% de la capacidad de la campaña</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>esta semana</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Autos</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>Google Ads</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Escalar SURA_AUTOS_PMAX (+30% budget) - CPA bajo $3.91</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>Subir presupuesto diario de 517,00 US$/día a +30%. Estrategia ya optimizada (Maximiza las conversiones).</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>CPA $3.91 entre los mejores del MCC. 2726 conversiones con $10,671 de inversion. Hay headroom para escalar antes de ver fatiga.</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>ALTO - +817 conversiones extra/mes a CPA similar</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
-        <is>
-          <t>hoy</t>
         </is>
       </c>
     </row>
